--- a/RC-template.xlsx
+++ b/RC-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ew-josh/Downloads/EW-Design/EW-WebView/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4588283-2857-3340-89E8-5A0A6B6DF6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84929075-A8EB-9E4F-803C-92959494607E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44040" yWindow="5360" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="12680" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t xml:space="preserve">Carrier Rate Confirmation        </t>
   </si>
@@ -92,9 +92,6 @@
   <si>
     <t>HOME BAY TRADING CORP is a property broker only, licensed with the FMCSA under MC# 1679494
 No pre-payment exists. We will pay your company by ACH, factoring of Apex Capital, RTS Financial, Bluff city when POD, invoice, delivery pictures, carrier collection account are ready. The quick payment requires a 3% handling fee, but monthly payment is free. Any individual collection account is not allowed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> EW</t>
   </si>
   <si>
     <t xml:space="preserve">Dispatcher : </t>
@@ -193,32 +190,7 @@
     <t>drop off ：</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Pick up：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+    <t>Pick up：</t>
   </si>
 </sst>
 </file>
@@ -1063,9 +1035,7 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="10"/>
-      <c r="I1" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" ht="20" x14ac:dyDescent="0.15">
       <c r="A2" s="4"/>
@@ -1074,7 +1044,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
@@ -1089,7 +1059,7 @@
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -1097,7 +1067,7 @@
     </row>
     <row r="4" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
@@ -1110,7 +1080,7 @@
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -1123,7 +1093,7 @@
     </row>
     <row r="6" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1136,7 +1106,7 @@
     </row>
     <row r="7" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
@@ -1223,14 +1193,14 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/RC-template.xlsx
+++ b/RC-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ew-josh/Downloads/EW-Design/EW-WebView/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84929075-A8EB-9E4F-803C-92959494607E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053AF822-1E99-AF47-BDFA-C65D1D37C776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="12680" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">Carrier Rate Confirmation        </t>
   </si>
@@ -185,12 +185,6 @@
   </si>
   <si>
     <t xml:space="preserve">Load Information: </t>
-  </si>
-  <si>
-    <t>drop off ：</t>
-  </si>
-  <si>
-    <t>Pick up：</t>
   </si>
 </sst>
 </file>
@@ -544,6 +538,30 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -588,30 +606,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1023,13 +1017,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
       <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
@@ -1043,94 +1037,90 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="94.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
     </row>
     <row r="5" spans="1:9" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="21"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="27"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23" t="s">
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="12" t="s">
         <v>5</v>
       </c>
@@ -1140,12 +1130,12 @@
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
@@ -1163,17 +1153,17 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3"/>
@@ -1188,11 +1178,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="A4:I4"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="A11:I11"/>
@@ -1201,6 +1186,11 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
